--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484360_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484360_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6615</v>
+        <v>8.247</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0246</v>
+        <v>5.5993</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6369</v>
+        <v>2.6476</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3837</v>
+        <v>4.231</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1062</v>
+        <v>1.2507</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2775</v>
+        <v>2.9803</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5339</v>
+        <v>4.3166</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7163</v>
+        <v>0.3914</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8176</v>
+        <v>3.9252</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1502</v>
+        <v>-0.0856</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3899</v>
+        <v>0.8593</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5401</v>
+        <v>-0.9449</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3674</v>
+        <v>2.3441</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8601</v>
+        <v>0.176</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6357</v>
+        <v>-0.0177</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2243</v>
+        <v>0.1938</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0503</v>
+        <v>1.4959</v>
       </c>
       <c r="W2" t="n">
-        <v>2.0503</v>
+        <v>1.4959</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.386699999999999</v>
+        <v>8.0924</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2761</v>
+        <v>6.7006</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1106</v>
+        <v>1.3918</v>
       </c>
       <c r="G3" t="n">
-        <v>4.231</v>
+        <v>4.3837</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2507</v>
+        <v>1.1062</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9803</v>
+        <v>3.2775</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3166</v>
+        <v>4.5339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3914</v>
+        <v>0.7163</v>
       </c>
       <c r="L3" t="n">
-        <v>3.9252</v>
+        <v>3.8176</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0856</v>
+        <v>-0.1502</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8593</v>
+        <v>0.3899</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9449</v>
+        <v>-0.5401</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5395</v>
+        <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3158</v>
+        <v>0.2909</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.341</v>
+        <v>0.3117</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6568000000000001</v>
+        <v>-0.0208</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4959</v>
+        <v>2.0503</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4959</v>
+        <v>2.0503</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7118</v>
+        <v>4.9168</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8988</v>
+        <v>4.0493</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8675</v>
       </c>
       <c r="G4" t="n">
         <v>3.5184</v>
@@ -766,13 +766,13 @@
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2167</v>
+        <v>0.4217</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.1439</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2233</v>
+        <v>0.2778</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.9135</v>
+        <v>3.8656</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7788</v>
+        <v>2.0304</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1348</v>
+        <v>1.8352</v>
       </c>
       <c r="G5" t="n">
         <v>1.1484</v>
@@ -844,13 +844,13 @@
         <v>2.7348</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8004</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8118</v>
+        <v>0.0634</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9886</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>2.16</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9935</v>
+        <v>1.8998</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6922</v>
+        <v>2.2989</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6987</v>
+        <v>-0.3991</v>
       </c>
       <c r="G6" t="n">
         <v>1.7152</v>
@@ -922,13 +922,13 @@
         <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2612</v>
+        <v>-0.3549</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.2406</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4139</v>
+        <v>-0.1143</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2186</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6679</v>
+        <v>1.0341</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0018</v>
+        <v>-0.8807</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6697</v>
+        <v>1.9148</v>
       </c>
       <c r="G7" t="n">
         <v>1.649</v>
@@ -1000,13 +1000,13 @@
         <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3951</v>
+        <v>-0.0289</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0221</v>
+        <v>0.1432</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4172</v>
+        <v>-0.1721</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.339</v>
+        <v>0.6641</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4519</v>
+        <v>0.6135</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1129</v>
+        <v>0.0505</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2503</v>
@@ -1078,13 +1078,13 @@
         <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0823</v>
+        <v>-0.7573</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5364</v>
+        <v>-0.3747</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.546</v>
+        <v>-0.3825</v>
       </c>
       <c r="V8" t="n">
         <v>0.4996</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1927</v>
+        <v>-1.6787</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0123</v>
+        <v>-1.689</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1804</v>
+        <v>0.0103</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9056</v>
@@ -1156,13 +1156,13 @@
         <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8964</v>
+        <v>-0.3824</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3494</v>
+        <v>-0.0261</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.547</v>
+        <v>-0.3564</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2542</v>
+        <v>-2.6203</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4909</v>
+        <v>-2.8842</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2367</v>
+        <v>0.264</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9009</v>
@@ -1234,13 +1234,13 @@
         <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5487</v>
+        <v>0.0853</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.1801</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2381</v>
+        <v>0.2654</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7189</v>
+        <v>-2.9773</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9986</v>
+        <v>-4.3114</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2797</v>
+        <v>1.3342</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7476</v>
@@ -1312,13 +1312,13 @@
         <v>2.3441</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4754</v>
+        <v>0.2662</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7125</v>
+        <v>-0.0254</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2371</v>
+        <v>0.2916</v>
       </c>
       <c r="V11" t="n">
         <v>0.3321</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9984</v>
+        <v>-4.0256</v>
       </c>
       <c r="E12" t="n">
         <v>-4.358</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3596</v>
+        <v>0.3324</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4</v>
@@ -1390,13 +1390,13 @@
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8133</v>
+        <v>-0.8405</v>
       </c>
       <c r="T12" t="n">
         <v>-0.4842</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3291</v>
+        <v>-0.3564</v>
       </c>
       <c r="V12" t="n">
         <v>0.3869</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.5097</v>
+        <v>17.4179</v>
       </c>
       <c r="E13" t="n">
-        <v>6.260799999999997</v>
+        <v>7.168700000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>10.249</v>
+        <v>10.2492</v>
       </c>
       <c r="G13" t="n">
         <v>7.441299999999998</v>
@@ -1468,13 +1468,13 @@
         <v>19.5343</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2794</v>
+        <v>-0.3714000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5946</v>
+        <v>-0.6866000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.315</v>
+        <v>0.3150999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>4.4876</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.404</v>
+        <v>5.7489</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1513</v>
+        <v>6.2524</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7473</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>4.7159</v>
@@ -1546,13 +1546,13 @@
         <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>0.356</v>
+        <v>0.7009</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1653</v>
+        <v>0.2664</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1907</v>
+        <v>0.4345</v>
       </c>
       <c r="V14" t="n">
         <v>0.3321</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5979</v>
+        <v>2.3476</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6568</v>
+        <v>1.3535</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9942</v>
       </c>
       <c r="G15" t="n">
         <v>1.5078</v>
@@ -1624,13 +1624,13 @@
         <v>0.1953</v>
       </c>
       <c r="S15" t="n">
-        <v>1.09</v>
+        <v>0.8398</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7484</v>
+        <v>0.4451</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3416</v>
+        <v>0.3948</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4787</v>
+        <v>1.3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4813</v>
+        <v>-0.1254</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9974</v>
+        <v>1.4255</v>
       </c>
       <c r="G16" t="n">
         <v>0.3187</v>
@@ -1702,13 +1702,13 @@
         <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8196</v>
+        <v>0.641</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3331</v>
+        <v>-0.2736</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4866</v>
+        <v>0.9146</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8317</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3535</v>
+        <v>0.3964</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1497</v>
+        <v>-0.0526</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2038</v>
+        <v>0.4489</v>
       </c>
       <c r="G17" t="n">
         <v>1.8715</v>
@@ -1780,13 +1780,13 @@
         <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4001</v>
+        <v>0.443</v>
       </c>
       <c r="T17" t="n">
-        <v>0.212</v>
+        <v>0.0098</v>
       </c>
       <c r="U17" t="n">
-        <v>0.188</v>
+        <v>0.4332</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9414</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4431</v>
+        <v>-0.6103</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0477</v>
+        <v>0.7443</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4908</v>
+        <v>-1.3546</v>
       </c>
       <c r="G18" t="n">
         <v>-0.138</v>
@@ -1858,13 +1858,13 @@
         <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3275</v>
+        <v>0.1603</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3715</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.044</v>
+        <v>0.0921</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2186</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5898</v>
+        <v>-0.9725</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1289</v>
+        <v>0.2301</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7187</v>
+        <v>-1.2026</v>
       </c>
       <c r="G19" t="n">
         <v>0.0702</v>
@@ -1936,13 +1936,13 @@
         <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9838</v>
+        <v>-0.3666</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.22</v>
+        <v>-0.1189</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7638</v>
+        <v>-0.2477</v>
       </c>
       <c r="V19" t="n">
         <v>0.8865</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7167</v>
+        <v>-1.6894</v>
       </c>
       <c r="E20" t="n">
         <v>-2.0277</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3111</v>
+        <v>0.3383</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7624</v>
@@ -2014,13 +2014,13 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5403</v>
+        <v>-0.5131</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4842</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0561</v>
+        <v>-0.0289</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6006</v>
+        <v>-2.8974</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1676</v>
+        <v>-0.572</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.433</v>
+        <v>-2.3254</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1917</v>
@@ -2092,13 +2092,13 @@
         <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5679</v>
+        <v>0.271</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9988</v>
+        <v>0.5944</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.431</v>
+        <v>-0.3234</v>
       </c>
       <c r="V21" t="n">
         <v>0.6093</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.5854</v>
+        <v>-9.2044</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.4846</v>
+        <v>-8.7768</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1008</v>
+        <v>-0.4276</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3738</v>
@@ -2170,13 +2170,13 @@
         <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1327</v>
+        <v>0.2482</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1362</v>
+        <v>-0.4284</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0034</v>
+        <v>0.6766</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6093</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.4084</v>
+        <v>-10.2546</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.184799999999999</v>
+        <v>-7.2748</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2235</v>
+        <v>-2.9798</v>
       </c>
       <c r="G23" t="n">
         <v>-7.4596</v>
@@ -2248,13 +2248,13 @@
         <v>2.5395</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6249</v>
+        <v>-0.4711</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.304</v>
+        <v>-0.3939</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.321</v>
+        <v>-0.0772</v>
       </c>
       <c r="V23" t="n">
         <v>-2.7145</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-16.5099</v>
+        <v>-15.8357</v>
       </c>
       <c r="E24" t="n">
         <v>-10.249</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.2608</v>
+        <v>-5.5866</v>
       </c>
       <c r="G24" t="n">
         <v>-7.441399999999999</v>
@@ -2326,13 +2326,13 @@
         <v>13.6739</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2794</v>
+        <v>1.9534</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3152999999999999</v>
+        <v>-0.3152</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5944</v>
+        <v>2.2686</v>
       </c>
       <c r="V24" t="n">
         <v>-4.4876</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484360_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484360_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,31 +819,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8656</v>
+        <v>3.2586</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0304</v>
+        <v>1.4234</v>
       </c>
       <c r="F5" t="n">
         <v>1.8352</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1484</v>
+        <v>0.5414</v>
       </c>
       <c r="H5" t="n">
         <v>1.9177</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7692</v>
+        <v>-1.3762</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1826</v>
+        <v>1.5756</v>
       </c>
       <c r="K5" t="n">
         <v>2.0069</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1757</v>
+        <v>-0.4313</v>
       </c>
       <c r="M5" t="n">
         <v>-1.0342</v>
@@ -860,6 +880,11 @@
       </c>
       <c r="X5" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,11 +1130,16 @@
       <c r="X8" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SERRA SÀNCHEZ</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6787</v>
+        <v>0.607</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.689</v>
+        <v>0.607</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0103</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9056</v>
+        <v>0.607</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0926</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9982</v>
+        <v>0.607</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4908</v>
+        <v>0.607</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1023</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4148</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0097</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3824</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0261</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3564</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1172,12 +1212,17 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>J. SERRA SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6203</v>
+        <v>-1.6787</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8842</v>
+        <v>-1.689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.264</v>
+        <v>0.0103</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9009</v>
+        <v>-0.9056</v>
       </c>
       <c r="H10" t="n">
-        <v>1.701</v>
+        <v>0.0926</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6018</v>
+        <v>-0.9982</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7507</v>
+        <v>-0.4908</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3111</v>
+        <v>0.1023</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0618</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1502</v>
+        <v>-0.4148</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3899</v>
+        <v>-0.0097</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5401</v>
+        <v>-0.4051</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0853</v>
+        <v>-0.3824</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1801</v>
+        <v>-0.0261</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2654</v>
+        <v>-0.3564</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9773</v>
+        <v>-2.6203</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3114</v>
+        <v>-2.8842</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3342</v>
+        <v>0.264</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.7476</v>
+        <v>-0.9009</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4843</v>
+        <v>1.701</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2633</v>
+        <v>-2.6018</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.3326</v>
+        <v>-0.7507</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.879</v>
+        <v>1.3111</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4536</v>
+        <v>-2.0618</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.415</v>
+        <v>-0.1502</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3948</v>
+        <v>0.3899</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8097</v>
+        <v>-0.5401</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2662</v>
+        <v>0.0853</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0254</v>
+        <v>-0.1801</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2916</v>
+        <v>0.2654</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MONTON MARTÍNEZ</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0256</v>
+        <v>-2.9773</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.358</v>
+        <v>-4.3114</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3324</v>
+        <v>1.3342</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4</v>
+        <v>-4.7476</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1481</v>
+        <v>-1.4843</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2519</v>
+        <v>-3.2633</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9204</v>
+        <v>-4.3326</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0614</v>
+        <v>-1.879</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9818</v>
+        <v>-2.4536</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4795</v>
+        <v>-0.415</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2095</v>
+        <v>0.3948</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.27</v>
+        <v>-0.8097</v>
       </c>
       <c r="P12" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8405</v>
+        <v>0.2662</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4842</v>
+        <v>-0.0254</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3564</v>
+        <v>0.2916</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3869</v>
+        <v>0.3321</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3869</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. MONTON MARTINEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.4179</v>
+        <v>-4.0256</v>
       </c>
       <c r="E13" t="n">
-        <v>7.168700000000002</v>
+        <v>-4.358</v>
       </c>
       <c r="F13" t="n">
-        <v>10.2492</v>
+        <v>0.3324</v>
       </c>
       <c r="G13" t="n">
-        <v>7.441299999999998</v>
+        <v>-2.4</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7654</v>
+        <v>-0.1481</v>
       </c>
       <c r="I13" t="n">
-        <v>0.676099999999999</v>
+        <v>-2.2519</v>
       </c>
       <c r="J13" t="n">
-        <v>12.6639</v>
+        <v>-1.9204</v>
       </c>
       <c r="K13" t="n">
-        <v>5.912</v>
+        <v>0.0614</v>
       </c>
       <c r="L13" t="n">
-        <v>6.751899999999999</v>
+        <v>-1.9818</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.2226</v>
+        <v>-0.4795</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8534000000000002</v>
+        <v>-0.2095</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.075699999999999</v>
+        <v>-0.27</v>
       </c>
       <c r="P13" t="n">
-        <v>5.860399999999998</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6739</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>19.5343</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3714000000000001</v>
+        <v>-0.8405</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6866000000000001</v>
+        <v>-0.4842</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3150999999999999</v>
+        <v>-0.3564</v>
       </c>
       <c r="V13" t="n">
-        <v>4.4876</v>
+        <v>0.3869</v>
       </c>
       <c r="W13" t="n">
-        <v>8.865500000000001</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.3778</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>DM GROUP MOLLET</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7489</v>
+        <v>17.4179</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2524</v>
+        <v>7.168700000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5034999999999999</v>
+        <v>10.2492</v>
       </c>
       <c r="G14" t="n">
-        <v>4.7159</v>
+        <v>7.441299999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5707</v>
+        <v>6.7654</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2866</v>
+        <v>0.676099999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>6.2249</v>
+        <v>12.6639</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.142</v>
+        <v>5.911999999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>6.3669</v>
+        <v>6.751900000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5091</v>
+        <v>-5.222599999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4287</v>
+        <v>0.8534000000000002</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0803</v>
+        <v>-6.075699999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.860399999999998</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3441</v>
+        <v>-13.6739</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3441</v>
+        <v>19.5343</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7009</v>
+        <v>-0.3714000000000003</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2664</v>
+        <v>-0.6866000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4345</v>
+        <v>0.3151</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3321</v>
+        <v>4.4876</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1052</v>
+        <v>8.865500000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7731</v>
-      </c>
+        <v>-4.3778</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DIAGNE YADE</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3476</v>
+        <v>5.7489</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3535</v>
+        <v>6.2524</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9942</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5078</v>
+        <v>4.7159</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7913</v>
+        <v>-0.5707</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2835</v>
+        <v>5.2866</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1038</v>
+        <v>6.2249</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9824000000000001</v>
+        <v>-0.142</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1214</v>
+        <v>6.3669</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4041</v>
+        <v>-1.5091</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8089</v>
+        <v>-0.4287</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4049</v>
+        <v>-1.0803</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>-2.3441</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1953</v>
+        <v>2.3441</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8398</v>
+        <v>0.7009</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4451</v>
+        <v>0.2664</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3948</v>
+        <v>0.4345</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>A. DIAGNE YADE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3</v>
+        <v>2.3476</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1254</v>
+        <v>1.3535</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4255</v>
+        <v>0.9942</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3187</v>
+        <v>1.5078</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.2571</v>
+        <v>1.7913</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5758</v>
+        <v>-0.2835</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3435</v>
+        <v>1.1038</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0195</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>1.363</v>
+        <v>0.1214</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0249</v>
+        <v>0.4041</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2377</v>
+        <v>0.8089</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2128</v>
+        <v>-0.4049</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>0.641</v>
+        <v>0.8398</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2736</v>
+        <v>0.4451</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9146</v>
+        <v>0.3948</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3964</v>
+        <v>1.3</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0526</v>
+        <v>-0.1254</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4489</v>
+        <v>1.4255</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8715</v>
+        <v>0.3187</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7391</v>
+        <v>-2.2571</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1324</v>
+        <v>2.5758</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>0.3435</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0466</v>
+        <v>-1.0195</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4035</v>
+        <v>1.363</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5785</v>
+        <v>-0.0249</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3075</v>
+        <v>-1.2377</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.271</v>
+        <v>1.2128</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1255</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>0.443</v>
+        <v>0.641</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0098</v>
+        <v>-0.2736</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4332</v>
+        <v>0.9146</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9414</v>
+        <v>-0.8317</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5545</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PERONA MARCH</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6103</v>
+        <v>0.3964</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7443</v>
+        <v>-0.0526</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3546</v>
+        <v>0.4489</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.138</v>
+        <v>1.8715</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9005</v>
+        <v>0.7391</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0385</v>
+        <v>1.1324</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6762</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3098</v>
+        <v>2.0466</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.4035</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8142</v>
+        <v>-1.5785</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4093</v>
+        <v>-1.3075</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4049</v>
+        <v>-0.271</v>
       </c>
       <c r="P18" t="n">
-        <v>0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R18" t="n">
-        <v>0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1603</v>
+        <v>0.443</v>
       </c>
       <c r="T18" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0098</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0921</v>
+        <v>0.4332</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2186</v>
+        <v>-0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>M. PERONA MARCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9725</v>
+        <v>-0.6103</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2301</v>
+        <v>0.7443</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2026</v>
+        <v>-1.3546</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0702</v>
+        <v>-0.138</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8667</v>
+        <v>0.9005</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7965</v>
+        <v>-1.0385</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9785</v>
+        <v>0.6762</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2906</v>
+        <v>1.3098</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6879</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9083</v>
+        <v>-0.8142</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4239</v>
+        <v>-0.4093</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4844</v>
+        <v>-0.4049</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3666</v>
+        <v>0.1603</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1189</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2477</v>
+        <v>0.0921</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8865</v>
+        <v>-1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6894</v>
+        <v>-0.9725</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0277</v>
+        <v>0.2301</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3383</v>
+        <v>-1.2026</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7624</v>
+        <v>0.0702</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3579</v>
+        <v>0.8667</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4045</v>
+        <v>-0.7965</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3482</v>
+        <v>1.9785</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6741</v>
+        <v>1.2906</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6741</v>
+        <v>0.6879</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4142</v>
+        <v>-1.9083</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6838</v>
+        <v>-0.4239</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2696</v>
+        <v>-1.4844</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1953</v>
+        <v>-3.1255</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5131</v>
+        <v>-0.3666</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4842</v>
+        <v>-0.1189</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0289</v>
+        <v>-0.2477</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8974</v>
+        <v>-1.6894</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.572</v>
+        <v>-2.0277</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3254</v>
+        <v>0.3383</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1917</v>
+        <v>-1.7624</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.669</v>
+        <v>-1.3579</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5227</v>
+        <v>-0.4045</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1581</v>
+        <v>-1.3482</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1986</v>
+        <v>-0.6741</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0405</v>
+        <v>-0.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0336</v>
+        <v>-0.4142</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5296</v>
+        <v>-0.6838</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.5632</v>
+        <v>0.2696</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>0.271</v>
+        <v>-0.5131</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5944</v>
+        <v>-0.4842</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3234</v>
+        <v>-0.0289</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.2044</v>
+        <v>-2.8974</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.7768</v>
+        <v>-0.572</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4276</v>
+        <v>-2.3254</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3738</v>
+        <v>-3.1917</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.3986</v>
+        <v>-0.669</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0249</v>
+        <v>-2.5227</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3161</v>
+        <v>-1.1581</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.612</v>
+        <v>-1.1986</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2959</v>
+        <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0577</v>
+        <v>-2.0336</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7866</v>
+        <v>0.5296</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.271</v>
+        <v>-2.5632</v>
       </c>
       <c r="P22" t="n">
-        <v>-5.4696</v>
+        <v>-0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-7.0323</v>
+        <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2482</v>
+        <v>0.271</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4284</v>
+        <v>0.5944</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6766</v>
+        <v>-0.3234</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6093</v>
+        <v>0.6093</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. REDA COLL</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.2546</v>
+        <v>-9.2044</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.2748</v>
+        <v>-8.7768</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9798</v>
+        <v>-0.4276</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.4596</v>
+        <v>-3.3738</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8094</v>
+        <v>-4.3986</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.6502</v>
+        <v>1.0249</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.7321</v>
+        <v>-1.3161</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8366</v>
+        <v>-2.612</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.8956</v>
+        <v>1.2959</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7275</v>
+        <v>-2.0577</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9729</v>
+        <v>-1.7866</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7546</v>
+        <v>-0.271</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3907</v>
+        <v>-5.4696</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1488</v>
+        <v>-7.0323</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5395</v>
+        <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4711</v>
+        <v>0.2482</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3939</v>
+        <v>-0.4284</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0772</v>
+        <v>0.6766</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.7145</v>
+        <v>-0.6093</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.7145</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. REDA COLL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,152 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-10.2546</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-7.2748</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.9798</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-7.4596</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.8094</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-5.6502</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-4.7321</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.8366</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-3.8956</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.7275</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.9729</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.7546</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.4711</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.3939</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.0772</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-2.7145</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.7145</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484360_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>-15.8357</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E25" t="n">
         <v>-10.249</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F25" t="n">
         <v>-5.5866</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G25" t="n">
         <v>-7.441399999999999</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H25" t="n">
         <v>-6.7651</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>-0.6762000000000006</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>5.222399999999999</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>-0.8533999999999999</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>6.075799999999999</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>-12.6639</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" t="n">
         <v>-5.9119</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O25" t="n">
         <v>-6.7519</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
         <v>-5.8602</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q25" t="n">
         <v>-19.5342</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>13.6739</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>1.9534</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>-0.3152</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>2.2686</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V25" t="n">
         <v>-4.4876</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W25" t="n">
         <v>4.378</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>-8.865500000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
